--- a/existing-spreadsheets/road_map_table_PT-BR.xlsx
+++ b/existing-spreadsheets/road_map_table_PT-BR.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="info" sheetId="1" r:id="R9ac8b27b0a424c62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agrouped" sheetId="2" r:id="R95956bdab1144f9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="info" sheetId="1" r:id="Re41ba875702d45b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agrouped" sheetId="2" r:id="Rc66a360840f04bd2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -318,7 +318,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="17">
+  <x:fonts count="19">
     <x:font>
       <x:sz val="10"/>
       <x:color rgb="FF000000"/>
@@ -400,8 +400,17 @@
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -448,8 +457,23 @@
         <x:fgColor rgb="FFF3F3F3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F1F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9D9D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="21">
+  <x:borders count="23">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -665,11 +689,39 @@
         <x:color indexed="1" rgb="FF000000"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF222222"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF222222"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF222222"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF222222"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF444444"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF444444"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF444444"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF444444"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="223">
+  <x:cellXfs count="263">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -1330,6 +1382,126 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1381,9 +1553,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3063,17 +3235,73 @@
         <x:v>https://www.gov.br/inpe/pt-br</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="15.75" customHeight="1">
-      <x:c r="C50" s="17"/>
-    </x:row>
-    <x:row r="51" ht="15.75" customHeight="1">
-      <x:c r="C51" s="17"/>
-    </x:row>
-    <x:row r="52" ht="15.75" customHeight="1">
-      <x:c r="C52" s="17"/>
-    </x:row>
-    <x:row r="53" ht="15.75" customHeight="1">
-      <x:c r="C53" s="17"/>
+    <x:row r="50" ht="53" customHeight="1">
+      <x:c r="A50" s="245" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B50" s="245" t="str">
+        <x:v>AEL Sistemas</x:v>
+      </x:c>
+      <x:c r="C50" s="247" t="str">
+        <x:v>Desenvolvimento, integração e produção de sistemas eletrônicos avançados, aviônica, radares e soluções de defesa; atuação específica em FPGA/RTL não confirmada pela fonte consultada.</x:v>
+      </x:c>
+      <x:c r="D50" s="245" t="str">
+        <x:v>Empresa privada (Nacional)</x:v>
+      </x:c>
+      <x:c r="E50" s="262" t="str">
+        <x:v>https://www.ael.com.br/sobre-nos/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="53" customHeight="1">
+      <x:c r="A51" s="245" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B51" s="245" t="str">
+        <x:v>Grupo Tellescom</x:v>
+      </x:c>
+      <x:c r="C51" s="247" t="str">
+        <x:v>Projeto de unidade de montagem, encapsulamento e testes de semicondutores em Cachoeirinha (RS), para aplicações automotivas, comunicações sem fio e IoT; fábrica ainda não operacional.</x:v>
+      </x:c>
+      <x:c r="D51" s="245" t="str">
+        <x:v>Empresa privada (Nacional)</x:v>
+      </x:c>
+      <x:c r="E51" s="262" t="str">
+        <x:v>https://tellescom.com.br/tellescom-mantem-projeto-para-instalar-fabrica-de-chips-de-r-1-bilhao-em-cachoeirinha/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="53" customHeight="1">
+      <x:c r="A52" s="245" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B52" s="245" t="str">
+        <x:v>OSIRIS</x:v>
+      </x:c>
+      <x:c r="C52" s="247" t="str">
+        <x:v>Grupo de pesquisa sem fins lucrativos voltado a arquiteturas RISC-V de código aberto, projeto de circuitos integrados digitais, IPs, SoCs e ASICs em VLSI.</x:v>
+      </x:c>
+      <x:c r="D52" s="245" t="str">
+        <x:v>Grupo de pesquisa sem fins lucrativos</x:v>
+      </x:c>
+      <x:c r="E52" s="262" t="str">
+        <x:v>https://www.osirisgroup.com.br/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="53" customHeight="1">
+      <x:c r="A53" s="245" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B53" s="245" t="str">
+        <x:v>Instituto SENAI (RS)</x:v>
+      </x:c>
+      <x:c r="C53" s="247" t="str">
+        <x:v>Pesquisa aplicada do SENAI-RS em eletrônica, sistemas de sensores, tecnologias embarcadas e inteligência artificial; projeto de FPGA/CI na unidade citada não confirmado especificamente.</x:v>
+      </x:c>
+      <x:c r="D53" s="245" t="str">
+        <x:v>Centro de pesquisas privado sem fins lucrativos</x:v>
+      </x:c>
+      <x:c r="E53" s="262" t="str">
+        <x:v>https://www.senairs.org.br/institutos/sistemas-de-sensoriamento</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="15.75" customHeight="1">
       <x:c r="C54" s="17"/>
@@ -4394,635 +4622,651 @@
     <x:col min="3" max="6" width="12.630000114440918" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="214" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="240" t="str">
         <x:v>nº</x:v>
       </x:c>
-      <x:c r="B1" s="214" t="str">
+      <x:c r="B1" s="240" t="str">
         <x:v>Empresa</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="218" t="str">
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="239" t="str">
         <x:v>Manaus</x:v>
       </x:c>
-      <x:c r="B2" s="219"/>
-    </x:row>
-    <x:row r="3" ht="20" customHeight="1">
-      <x:c r="A3" s="222" t="n">
+      <x:c r="B2" s="239"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="236" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B3" s="222" t="str">
+      <x:c r="B3" s="236" t="str">
         <x:v>Instituto SENAI de Inovação em Microeletrônica</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="20" customHeight="1">
-      <x:c r="A4" s="222" t="n">
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="236" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B4" s="222" t="str">
+      <x:c r="B4" s="236" t="str">
         <x:v>ADATA</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="20" customHeight="1">
-      <x:c r="A5" s="222" t="n">
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="236" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B5" s="222" t="str">
+      <x:c r="B5" s="236" t="str">
         <x:v>Zilia</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="20" customHeight="1">
-      <x:c r="A6" s="222" t="n">
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="236" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B6" s="222" t="str">
+      <x:c r="B6" s="236" t="str">
         <x:v>Stoneridge</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="20" customHeight="1">
-      <x:c r="A7" s="222" t="n">
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="236" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B7" s="222" t="str">
+      <x:c r="B7" s="236" t="str">
         <x:v>HBR</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="20" customHeight="1">
-      <x:c r="A8" s="222" t="n">
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="236" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B8" s="222" t="str">
+      <x:c r="B8" s="236" t="str">
         <x:v>Instituto de Pesquisas ELDORADO</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="20" customHeight="1">
-      <x:c r="A9" s="222" t="n">
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="236" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B9" s="222" t="str">
+      <x:c r="B9" s="236" t="str">
         <x:v>HT Micron</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="20" customHeight="1">
-      <x:c r="A10" s="222" t="n">
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="236" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B10" s="222" t="str">
+      <x:c r="B10" s="236" t="str">
         <x:v>CCBS / TERA</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="218" t="str">
+    <x:row r="11" ht="28" customHeight="1">
+      <x:c r="A11" s="239" t="str">
         <x:v>Brasília</x:v>
       </x:c>
-      <x:c r="B11" s="219"/>
-    </x:row>
-    <x:row r="12" ht="20" customHeight="1">
-      <x:c r="A12" s="222" t="n">
+      <x:c r="B11" s="239"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="236" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B12" s="222" t="str">
+      <x:c r="B12" s="236" t="str">
         <x:v>HBR</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="20" customHeight="1">
-      <x:c r="A13" s="222" t="n">
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="236" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B13" s="222" t="str">
+      <x:c r="B13" s="236" t="str">
         <x:v>Instituto de Pesquisas ELDORADO</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="220" t="str">
+    <x:row r="14" ht="28" customHeight="1">
+      <x:c r="A14" s="239" t="str">
         <x:v>Campina Grande</x:v>
       </x:c>
-      <x:c r="B14" s="221"/>
-    </x:row>
-    <x:row r="15" ht="20" customHeight="1">
-      <x:c r="A15" s="222" t="n">
+      <x:c r="B14" s="239"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="236" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B15" s="222" t="str">
+      <x:c r="B15" s="236" t="str">
         <x:v>HWiT</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="220" t="str">
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="239" t="str">
         <x:v>Salvador</x:v>
       </x:c>
-      <x:c r="B16" s="221"/>
-    </x:row>
-    <x:row r="17" ht="20" customHeight="1">
-      <x:c r="A17" s="222" t="n">
+      <x:c r="B16" s="239"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="236" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B17" s="222" t="str">
+      <x:c r="B17" s="236" t="str">
         <x:v>SENAI CIMATEC</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="20" customHeight="1">
-      <x:c r="A18" s="222" t="n">
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="236" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B18" s="222" t="str">
+      <x:c r="B18" s="236" t="str">
         <x:v>HBR</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="24" customHeight="1">
-      <x:c r="A19" s="220" t="str">
+    <x:row r="19" ht="28" customHeight="1">
+      <x:c r="A19" s="239" t="str">
         <x:v>Interior de Minas Gerais</x:v>
       </x:c>
-      <x:c r="B19" s="221"/>
-    </x:row>
-    <x:row r="20" ht="20" customHeight="1">
-      <x:c r="A20" s="222" t="n">
+      <x:c r="B19" s="239"/>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="236" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B20" s="222" t="str">
+      <x:c r="B20" s="236" t="str">
         <x:v>LC-e</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="20" customHeight="1">
-      <x:c r="A21" s="222" t="n">
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="236" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B21" s="222" t="str">
+      <x:c r="B21" s="236" t="str">
         <x:v>Inatel</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="20" customHeight="1">
-      <x:c r="A22" s="222" t="n">
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="236" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B22" s="222" t="str">
+      <x:c r="B22" s="236" t="str">
         <x:v>Modirum | GESPI</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="20" customHeight="1">
-      <x:c r="A23" s="222" t="n">
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="236" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B23" s="222" t="str">
+      <x:c r="B23" s="236" t="str">
         <x:v>Marelli</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="20" customHeight="1">
-      <x:c r="A24" s="222" t="n">
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="236" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B24" s="222" t="str">
+      <x:c r="B24" s="236" t="str">
         <x:v>Stellantis</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="20" customHeight="1">
-      <x:c r="A25" s="222" t="n">
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="236" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B25" s="222" t="str">
+      <x:c r="B25" s="236" t="str">
         <x:v>Multilaser</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="24" customHeight="1">
-      <x:c r="A26" s="220" t="str">
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="A26" s="239" t="str">
         <x:v>Belo Horizonte e proximidades</x:v>
       </x:c>
-      <x:c r="B26" s="221"/>
-    </x:row>
-    <x:row r="27" ht="20" customHeight="1">
-      <x:c r="A27" s="222" t="n">
+      <x:c r="B26" s="239"/>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="236" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B27" s="222" t="str">
+      <x:c r="B27" s="236" t="str">
         <x:v>Cadence</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="20" customHeight="1">
-      <x:c r="A28" s="222" t="n">
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="236" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B28" s="222" t="str">
+      <x:c r="B28" s="236" t="str">
         <x:v>RFIDO Design</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="24" customHeight="1">
-      <x:c r="A29" s="220" t="str">
+    <x:row r="29" ht="28" customHeight="1">
+      <x:c r="A29" s="239" t="str">
         <x:v>Campinas e proximidades</x:v>
       </x:c>
-      <x:c r="B29" s="221"/>
-    </x:row>
-    <x:row r="30" ht="20" customHeight="1">
-      <x:c r="A30" s="222" t="n">
+      <x:c r="B29" s="239"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="236" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B30" s="222" t="str">
+      <x:c r="B30" s="236" t="str">
         <x:v>Von Braun Labs</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="20" customHeight="1">
-      <x:c r="A31" s="222" t="n">
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="236" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B31" s="222" t="str">
+      <x:c r="B31" s="236" t="str">
         <x:v>ADATA</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="20" customHeight="1">
-      <x:c r="A32" s="222" t="n">
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="236" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B32" s="222" t="str">
+      <x:c r="B32" s="236" t="str">
         <x:v>HBR</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="20" customHeight="1">
-      <x:c r="A33" s="222" t="n">
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="236" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B33" s="222" t="str">
+      <x:c r="B33" s="236" t="str">
         <x:v>HWiT</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="20" customHeight="1">
-      <x:c r="A34" s="222" t="n">
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="236" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B34" s="222" t="str">
+      <x:c r="B34" s="236" t="str">
         <x:v>EnSilica</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="20" customHeight="1">
-      <x:c r="A35" s="222" t="n">
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="236" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B35" s="222" t="str">
+      <x:c r="B35" s="236" t="str">
         <x:v>CPQD</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="20" customHeight="1">
-      <x:c r="A36" s="222" t="n">
+    <x:row r="36" ht="24" customHeight="1">
+      <x:c r="A36" s="236" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B36" s="222" t="str">
+      <x:c r="B36" s="236" t="str">
         <x:v>Aedvices</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="20" customHeight="1">
-      <x:c r="A37" s="222" t="n">
+    <x:row r="37" ht="24" customHeight="1">
+      <x:c r="A37" s="236" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B37" s="222" t="str">
+      <x:c r="B37" s="236" t="str">
         <x:v>Instituto de Pesquisas ELDORADO</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="20" customHeight="1">
-      <x:c r="A38" s="222" t="n">
+    <x:row r="38" ht="24" customHeight="1">
+      <x:c r="A38" s="236" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B38" s="222" t="str">
+      <x:c r="B38" s="236" t="str">
         <x:v>Stoneridge</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="20" customHeight="1">
-      <x:c r="A39" s="222" t="n">
+    <x:row r="39" ht="24" customHeight="1">
+      <x:c r="A39" s="236" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B39" s="222" t="str">
+      <x:c r="B39" s="236" t="str">
         <x:v>Valeo</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="20" customHeight="1">
-      <x:c r="A40" s="222" t="n">
+    <x:row r="40" ht="24" customHeight="1">
+      <x:c r="A40" s="236" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B40" s="222" t="str">
+      <x:c r="B40" s="236" t="str">
         <x:v>Cadence</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="20" customHeight="1">
-      <x:c r="A41" s="222" t="n">
+    <x:row r="41" ht="24" customHeight="1">
+      <x:c r="A41" s="236" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B41" s="222" t="str">
+      <x:c r="B41" s="236" t="str">
         <x:v>CNPEM</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="20" customHeight="1">
-      <x:c r="A42" s="222" t="n">
+    <x:row r="42" ht="24" customHeight="1">
+      <x:c r="A42" s="236" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B42" s="222" t="str">
+      <x:c r="B42" s="236" t="str">
         <x:v>CTI Renato Archer</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="20" customHeight="1">
-      <x:c r="A43" s="222" t="n">
+    <x:row r="43" ht="24" customHeight="1">
+      <x:c r="A43" s="236" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B43" s="222" t="str">
+      <x:c r="B43" s="236" t="str">
         <x:v>HCLTech</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="24" customHeight="1">
-      <x:c r="A44" s="218" t="str">
+    <x:row r="44" ht="28" customHeight="1">
+      <x:c r="A44" s="239" t="str">
         <x:v>Florianópolis</x:v>
       </x:c>
-      <x:c r="B44" s="219"/>
-    </x:row>
-    <x:row r="45" ht="20" customHeight="1">
-      <x:c r="A45" s="222" t="n">
+      <x:c r="B44" s="239"/>
+    </x:row>
+    <x:row r="45" ht="24" customHeight="1">
+      <x:c r="A45" s="236" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B45" s="222" t="str">
+      <x:c r="B45" s="236" t="str">
         <x:v>Macnica DHW</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="20" customHeight="1">
-      <x:c r="A46" s="222" t="n">
+    <x:row r="46" ht="24" customHeight="1">
+      <x:c r="A46" s="236" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B46" s="222" t="str">
+      <x:c r="B46" s="236" t="str">
+        <x:v>Chipus</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="24" customHeight="1">
+      <x:c r="A47" s="236" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B47" s="236" t="str">
+        <x:v>Synopsys</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="24" customHeight="1">
+      <x:c r="A48" s="236" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B48" s="236" t="str">
+        <x:v>OSIRIS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="24" customHeight="1">
+      <x:c r="A49" s="236" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B49" s="236" t="str">
         <x:v>Silicium</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="20" customHeight="1">
-      <x:c r="A47" s="222" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B47" s="222" t="str">
-        <x:v>Chipus</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" ht="20" customHeight="1">
-      <x:c r="A48" s="222" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B48" s="222" t="str">
-        <x:v>Synopsys</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="24" customHeight="1">
-      <x:c r="A49" s="220" t="str">
+    <x:row r="50" ht="28" customHeight="1">
+      <x:c r="A50" s="239" t="str">
         <x:v>Porto Alegre e proximidades</x:v>
       </x:c>
-      <x:c r="B49" s="221"/>
-    </x:row>
-    <x:row r="50" ht="20" customHeight="1">
-      <x:c r="A50" s="222" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B50" s="222" t="str">
+      <x:c r="B50" s="239"/>
+    </x:row>
+    <x:row r="51" ht="24" customHeight="1">
+      <x:c r="A51" s="236" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B51" s="236" t="str">
+        <x:v>Impinj</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="24" customHeight="1">
+      <x:c r="A52" s="236" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B52" s="236" t="str">
+        <x:v>SILVACO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="24" customHeight="1">
+      <x:c r="A53" s="236" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B53" s="236" t="str">
+        <x:v>HCLTech</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="24" customHeight="1">
+      <x:c r="A54" s="236" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B54" s="236" t="str">
+        <x:v>AEL Sistemas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="24" customHeight="1">
+      <x:c r="A55" s="236" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B55" s="236" t="str">
+        <x:v>Grupo Tellescom</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="24" customHeight="1">
+      <x:c r="A56" s="236" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B56" s="236" t="str">
+        <x:v>Valeo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="24" customHeight="1">
+      <x:c r="A57" s="236" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B57" s="236" t="str">
+        <x:v>Instituto de Pesquisas ELDORADO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="24" customHeight="1">
+      <x:c r="A58" s="236" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B58" s="236" t="str">
+        <x:v>EnSilica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="236" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B59" s="236" t="str">
+        <x:v>itt Chip — Unisinos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="24" customHeight="1">
+      <x:c r="A60" s="236" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B60" s="236" t="str">
+        <x:v>CEITEC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="24" customHeight="1">
+      <x:c r="A61" s="236" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B61" s="236" t="str">
+        <x:v>Instituto SENAI (RS)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="24" customHeight="1">
+      <x:c r="A62" s="236" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B62" s="236" t="str">
+        <x:v>InPlace</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="24" customHeight="1">
+      <x:c r="A63" s="236" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B63" s="236" t="str">
         <x:v>HT Micron</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="20" customHeight="1">
-      <x:c r="A51" s="222" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B51" s="222" t="str">
-        <x:v>Impinj</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" ht="20" customHeight="1">
-      <x:c r="A52" s="222" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B52" s="222" t="str">
-        <x:v>SILVACO</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="20" customHeight="1">
-      <x:c r="A53" s="222" t="n">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B53" s="222" t="str">
+    <x:row r="64" ht="28" customHeight="1">
+      <x:c r="A64" s="239" t="str">
+        <x:v>Interior de São Paulo</x:v>
+      </x:c>
+      <x:c r="B64" s="239"/>
+    </x:row>
+    <x:row r="65" ht="24" customHeight="1">
+      <x:c r="A65" s="236" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B65" s="236" t="str">
+        <x:v>Macnica DHW</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="24" customHeight="1">
+      <x:c r="A66" s="236" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B66" s="236" t="str">
+        <x:v>WG3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="24" customHeight="1">
+      <x:c r="A67" s="236" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B67" s="236" t="str">
+        <x:v>Chip Inventor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="24" customHeight="1">
+      <x:c r="A68" s="236" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B68" s="236" t="str">
+        <x:v>Beontag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="24" customHeight="1">
+      <x:c r="A69" s="236" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B69" s="236" t="str">
+        <x:v>SPICTEC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="24" customHeight="1">
+      <x:c r="A70" s="236" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B70" s="236" t="str">
+        <x:v>LSI-TEC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="28" customHeight="1">
+      <x:c r="A71" s="239" t="str">
+        <x:v>Curitiba e proximidades</x:v>
+      </x:c>
+      <x:c r="B71" s="239"/>
+    </x:row>
+    <x:row r="72" ht="24" customHeight="1">
+      <x:c r="A72" s="236" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B72" s="236" t="str">
         <x:v>HCLTech</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="20" customHeight="1">
-      <x:c r="A54" s="222" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B54" s="222" t="str">
-        <x:v>Valeo</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" ht="20" customHeight="1">
-      <x:c r="A55" s="222" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B55" s="222" t="str">
-        <x:v>Instituto de Pesquisas ELDORADO</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="20" customHeight="1">
-      <x:c r="A56" s="222" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B56" s="222" t="str">
-        <x:v>EnSilica</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="20" customHeight="1">
-      <x:c r="A57" s="222" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B57" s="222" t="str">
-        <x:v>itt Chip — Unisinos</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="20" customHeight="1">
-      <x:c r="A58" s="222" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B58" s="222" t="str">
-        <x:v>CEITEC</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="20" customHeight="1">
-      <x:c r="A59" s="222" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B59" s="222" t="str">
-        <x:v>InPlace</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="24" customHeight="1">
-      <x:c r="A60" s="218" t="str">
-        <x:v>Interior de São Paulo</x:v>
-      </x:c>
-      <x:c r="B60" s="219"/>
-    </x:row>
-    <x:row r="61" ht="20" customHeight="1">
-      <x:c r="A61" s="222" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B61" s="222" t="str">
-        <x:v>LSI-TEC</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="20" customHeight="1">
-      <x:c r="A62" s="222" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B62" s="222" t="str">
-        <x:v>Macnica DHW</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="20" customHeight="1">
-      <x:c r="A63" s="222" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B63" s="222" t="str">
-        <x:v>WG3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="20" customHeight="1">
-      <x:c r="A64" s="222" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B64" s="222" t="str">
-        <x:v>Chip Inventor</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="20" customHeight="1">
-      <x:c r="A65" s="222" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B65" s="222" t="str">
-        <x:v>Beontag</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="20" customHeight="1">
-      <x:c r="A66" s="222" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B66" s="222" t="str">
-        <x:v>SPICTEC</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="24" customHeight="1">
-      <x:c r="A67" s="218" t="str">
-        <x:v>Curitiba e proximidades</x:v>
-      </x:c>
-      <x:c r="B67" s="219"/>
-    </x:row>
-    <x:row r="68" ht="20" customHeight="1">
-      <x:c r="A68" s="222" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B68" s="222" t="str">
+    <x:row r="73" ht="24" customHeight="1">
+      <x:c r="A73" s="236" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B73" s="236" t="str">
         <x:v>Thales Group</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="20" customHeight="1">
-      <x:c r="A69" s="222" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B69" s="222" t="str">
-        <x:v>HCLTech</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" ht="24" customHeight="1">
-      <x:c r="A70" s="218" t="str">
+    <x:row r="74" ht="28" customHeight="1">
+      <x:c r="A74" s="239" t="str">
         <x:v>Interior do Rio Grande do Sul</x:v>
       </x:c>
-      <x:c r="B70" s="219"/>
-    </x:row>
-    <x:row r="71" ht="20" customHeight="1">
-      <x:c r="A71" s="222" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B71" s="222" t="str">
+      <x:c r="B74" s="239"/>
+    </x:row>
+    <x:row r="75" ht="24" customHeight="1">
+      <x:c r="A75" s="236" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B75" s="236" t="str">
+        <x:v>TUNA Semicondutores</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="24" customHeight="1">
+      <x:c r="A76" s="236" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B76" s="236" t="str">
         <x:v>GMicro UFSM</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="20" customHeight="1">
-      <x:c r="A72" s="222" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B72" s="222" t="str">
-        <x:v>TUNA Semicondutores</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="24" customHeight="1">
-      <x:c r="A73" s="218" t="str">
+    <x:row r="77" ht="28" customHeight="1">
+      <x:c r="A77" s="239" t="str">
         <x:v>São José dos Campos e proximidades</x:v>
       </x:c>
-      <x:c r="B73" s="219"/>
-    </x:row>
-    <x:row r="74" ht="20" customHeight="1">
-      <x:c r="A74" s="222" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B74" s="222" t="str">
+      <x:c r="B77" s="239"/>
+    </x:row>
+    <x:row r="78" ht="24" customHeight="1">
+      <x:c r="A78" s="236" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B78" s="236" t="str">
+        <x:v>Boeing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="24" customHeight="1">
+      <x:c r="A79" s="236" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B79" s="236" t="str">
+        <x:v>Embraer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="24" customHeight="1">
+      <x:c r="A80" s="236" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B80" s="236" t="str">
+        <x:v>Thales Group</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="24" customHeight="1">
+      <x:c r="A81" s="237" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B81" s="237" t="str">
         <x:v>SIATT</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="20" customHeight="1">
-      <x:c r="A75" s="222" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B75" s="222" t="str">
+    <x:row r="82" ht="24" customHeight="1">
+      <x:c r="A82" s="237" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B82" s="237" t="str">
         <x:v>IACIT</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="20" customHeight="1">
-      <x:c r="A76" s="222" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B76" s="222" t="str">
+    <x:row r="83" ht="24" customHeight="1">
+      <x:c r="A83" s="237" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B83" s="237" t="str">
         <x:v>INPE</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="20" customHeight="1">
-      <x:c r="A77" s="222" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B77" s="222" t="str">
+    <x:row r="84" ht="24" customHeight="1">
+      <x:c r="A84" s="237" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B84" s="237" t="str">
         <x:v>Modirum | GESPI</x:v>
       </x:c>
-    </x:row>
-    <x:row r="78" ht="20" customHeight="1">
-      <x:c r="A78" s="222" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B78" s="222" t="str">
-        <x:v>Boeing</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="20" customHeight="1">
-      <x:c r="A79" s="222" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B79" s="222" t="str">
-        <x:v>Embraer</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="20" customHeight="1">
-      <x:c r="A80" s="222" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B80" s="222" t="str">
-        <x:v>Thales Group</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="15.75" customHeight="1">
-      <x:c r="A81" s="20"/>
-      <x:c r="B81" s="20"/>
-    </x:row>
-    <x:row r="82" ht="15.75" customHeight="1">
-      <x:c r="A82" s="20"/>
-      <x:c r="B82" s="20"/>
-    </x:row>
-    <x:row r="83" ht="15.75" customHeight="1">
-      <x:c r="A83" s="20"/>
-      <x:c r="B83" s="20"/>
-    </x:row>
-    <x:row r="84" ht="15.75" customHeight="1">
-      <x:c r="A84" s="20"/>
-      <x:c r="B84" s="20"/>
     </x:row>
     <x:row r="85" ht="15.75" customHeight="1">
       <x:c r="A85" s="20"/>
@@ -6484,11 +6728,11 @@
     <x:mergeCell ref="A26:B26"/>
     <x:mergeCell ref="A29:B29"/>
     <x:mergeCell ref="A44:B44"/>
-    <x:mergeCell ref="A49:B49"/>
-    <x:mergeCell ref="A60:B60"/>
-    <x:mergeCell ref="A67:B67"/>
-    <x:mergeCell ref="A70:B70"/>
-    <x:mergeCell ref="A73:B73"/>
+    <x:mergeCell ref="A50:B50"/>
+    <x:mergeCell ref="A64:B64"/>
+    <x:mergeCell ref="A71:B71"/>
+    <x:mergeCell ref="A74:B74"/>
+    <x:mergeCell ref="A77:B77"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/existing-spreadsheets/road_map_table_PT-BR.xlsx
+++ b/existing-spreadsheets/road_map_table_PT-BR.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="info" sheetId="1" r:id="Re41ba875702d45b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agrouped" sheetId="2" r:id="Rc66a360840f04bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="info" sheetId="1" r:id="R0235a2d10e7844f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agrouped" sheetId="2" r:id="Rcddeee33ac36401d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -281,12 +281,6 @@
     <x:t xml:space="preserve">Zilia</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Fabricação, encapsulamento e teste de circuitos integrados de memória e módulos; pouco foco em desenvolvimento FPGA/RTL.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://ziliatech.com/institucional/</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ADATA</x:t>
   </x:si>
   <x:si>
@@ -318,7 +312,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="19">
+  <x:fonts count="23">
     <x:font>
       <x:sz val="10"/>
       <x:color rgb="FF000000"/>
@@ -409,8 +403,27 @@
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0563C1"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="13">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -470,6 +483,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9D9D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E7E7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -721,7 +744,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="263">
+  <x:cellXfs count="289">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -1501,6 +1524,84 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2738,14 +2839,14 @@
       <x:c r="B29" s="215" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="C29" s="216" t="s">
-        <x:v>90</x:v>
+      <x:c r="C29" s="216" t="str">
+        <x:v>Encapsulamento, testes e manufatura de circuitos integrados de memória (DRAM/Flash) em Atibaia/SP; montagem de módulos em Manaus/AM e P&amp;D em parceria com o Eldorado em Campinas/SP. Equipe própria de RTL/FPGA não confirmada.</x:v>
       </x:c>
       <x:c r="D29" s="215" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E29" s="217" t="s">
-        <x:v>91</x:v>
+      <x:c r="E29" s="217" t="str">
+        <x:v>https://ziliatech.com/unidades/ | https://ziliatech.com/institucional/</x:v>
       </x:c>
       <x:c r="F29" s="4"/>
       <x:c r="G29" s="4"/>
@@ -2774,16 +2875,16 @@
         <x:v>29.0</x:v>
       </x:c>
       <x:c r="B30" s="215" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C30" s="216" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D30" s="215" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E30" s="217" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F30" s="4"/>
       <x:c r="G30" s="4"/>
@@ -2812,16 +2913,16 @@
         <x:v>30.0</x:v>
       </x:c>
       <x:c r="B31" s="215" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C31" s="216" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D31" s="215" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E31" s="217" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F31" s="4"/>
       <x:c r="G31" s="4"/>
@@ -2850,16 +2951,16 @@
         <x:v>31.0</x:v>
       </x:c>
       <x:c r="B32" s="215" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C32" s="216" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D32" s="215" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E32" s="217" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F32" s="4"/>
       <x:c r="G32" s="4"/>
@@ -3303,11 +3404,39 @@
         <x:v>https://www.senairs.org.br/institutos/sistemas-de-sensoriamento</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="15.75" customHeight="1">
-      <x:c r="C54" s="17"/>
-    </x:row>
-    <x:row r="55" ht="15.75" customHeight="1">
-      <x:c r="C55" s="17"/>
+    <x:row r="54" ht="60" customHeight="1">
+      <x:c r="A54" s="284" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B54" s="284" t="str">
+        <x:v>Tecsys do Brasil</x:v>
+      </x:c>
+      <x:c r="C54" s="286" t="str">
+        <x:v>Desenvolvimento de sistemas eletrônicos e hardware digital para TV digital/broadcast, RF, telecomunicações, automação embarcada e smart grid; utilização de FPGA documentada em equipamento próprio. Projeto de ASIC não confirmado.</x:v>
+      </x:c>
+      <x:c r="D54" s="284" t="str">
+        <x:v>Empresa privada (Nacional)</x:v>
+      </x:c>
+      <x:c r="E54" s="288" t="str">
+        <x:v>https://www.tecsysbrasil.com.br/sobre/ | https://www.tecsysbrasil.com.br/produtos/broadcast/manuais/MAN_TS9600_RMX_IP.pdf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="60" customHeight="1">
+      <x:c r="A55" s="284" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B55" s="284" t="str">
+        <x:v>Lactec</x:v>
+      </x:c>
+      <x:c r="C55" s="286" t="str">
+        <x:v>PD&amp;I em hardware e eletrônica embarcada, sistemas com microprocessadores, firmware, sensores, IA embarcada e smart grids; equipe específica de projeto FPGA/ASIC não confirmada publicamente.</x:v>
+      </x:c>
+      <x:c r="D55" s="284" t="str">
+        <x:v>Centro de pesquisas privado sem fins lucrativos</x:v>
+      </x:c>
+      <x:c r="E55" s="288" t="str">
+        <x:v>https://lactec.com.br/solucoes/pdi/embrapii/ | https://lactec.com.br/quem-somos/</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="15.75" customHeight="1">
       <x:c r="C56" s="17"/>
@@ -4630,655 +4759,667 @@
         <x:v>Empresa</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="239" t="str">
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="275" t="str">
         <x:v>Manaus</x:v>
       </x:c>
-      <x:c r="B2" s="239"/>
+      <x:c r="B2" s="275"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="236" t="n">
+      <x:c r="A3" s="271" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B3" s="236" t="str">
+      <x:c r="B3" s="271" t="str">
         <x:v>Instituto SENAI de Inovação em Microeletrônica</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="236" t="n">
+      <x:c r="A4" s="271" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B4" s="236" t="str">
+      <x:c r="B4" s="271" t="str">
         <x:v>ADATA</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="236" t="n">
+      <x:c r="A5" s="271" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B5" s="236" t="str">
+      <x:c r="B5" s="271" t="str">
         <x:v>Zilia</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="236" t="n">
+      <x:c r="A6" s="271" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B6" s="236" t="str">
+      <x:c r="B6" s="271" t="str">
         <x:v>Stoneridge</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="236" t="n">
+      <x:c r="A7" s="271" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B7" s="236" t="str">
+      <x:c r="B7" s="271" t="str">
         <x:v>HBR</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="236" t="n">
+      <x:c r="A8" s="271" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B8" s="236" t="str">
+      <x:c r="B8" s="271" t="str">
         <x:v>Instituto de Pesquisas ELDORADO</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="236" t="n">
+      <x:c r="A9" s="271" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B9" s="236" t="str">
+      <x:c r="B9" s="271" t="str">
         <x:v>HT Micron</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="236" t="n">
+      <x:c r="A10" s="271" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B10" s="236" t="str">
+      <x:c r="B10" s="271" t="str">
         <x:v>CCBS / TERA</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="28" customHeight="1">
-      <x:c r="A11" s="239" t="str">
+    <x:row r="11" ht="27" customHeight="1">
+      <x:c r="A11" s="275" t="str">
         <x:v>Brasília</x:v>
       </x:c>
-      <x:c r="B11" s="239"/>
+      <x:c r="B11" s="275"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="236" t="n">
+      <x:c r="A12" s="271" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B12" s="236" t="str">
+      <x:c r="B12" s="271" t="str">
         <x:v>HBR</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="236" t="n">
+      <x:c r="A13" s="271" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B13" s="236" t="str">
+      <x:c r="B13" s="271" t="str">
         <x:v>Instituto de Pesquisas ELDORADO</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="239" t="str">
+    <x:row r="14" ht="27" customHeight="1">
+      <x:c r="A14" s="275" t="str">
         <x:v>Campina Grande</x:v>
       </x:c>
-      <x:c r="B14" s="239"/>
+      <x:c r="B14" s="275"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="236" t="n">
+      <x:c r="A15" s="271" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B15" s="236" t="str">
+      <x:c r="B15" s="271" t="str">
         <x:v>HWiT</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="239" t="str">
+    <x:row r="16" ht="27" customHeight="1">
+      <x:c r="A16" s="275" t="str">
         <x:v>Salvador</x:v>
       </x:c>
-      <x:c r="B16" s="239"/>
+      <x:c r="B16" s="275"/>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="236" t="n">
+      <x:c r="A17" s="271" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B17" s="236" t="str">
+      <x:c r="B17" s="271" t="str">
         <x:v>SENAI CIMATEC</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
-      <x:c r="A18" s="236" t="n">
+      <x:c r="A18" s="271" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B18" s="236" t="str">
+      <x:c r="B18" s="271" t="str">
         <x:v>HBR</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="28" customHeight="1">
-      <x:c r="A19" s="239" t="str">
+    <x:row r="19" ht="27" customHeight="1">
+      <x:c r="A19" s="275" t="str">
         <x:v>Interior de Minas Gerais</x:v>
       </x:c>
-      <x:c r="B19" s="239"/>
+      <x:c r="B19" s="275"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="236" t="n">
+      <x:c r="A20" s="271" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B20" s="236" t="str">
+      <x:c r="B20" s="271" t="str">
         <x:v>LC-e</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
-      <x:c r="A21" s="236" t="n">
+      <x:c r="A21" s="271" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B21" s="236" t="str">
+      <x:c r="B21" s="271" t="str">
         <x:v>Inatel</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="236" t="n">
+      <x:c r="A22" s="271" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B22" s="236" t="str">
+      <x:c r="B22" s="271" t="str">
         <x:v>Modirum | GESPI</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
-      <x:c r="A23" s="236" t="n">
+      <x:c r="A23" s="271" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B23" s="236" t="str">
+      <x:c r="B23" s="271" t="str">
         <x:v>Marelli</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="236" t="n">
+      <x:c r="A24" s="271" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B24" s="236" t="str">
+      <x:c r="B24" s="271" t="str">
         <x:v>Stellantis</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
-      <x:c r="A25" s="236" t="n">
+      <x:c r="A25" s="271" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B25" s="236" t="str">
+      <x:c r="B25" s="271" t="str">
         <x:v>Multilaser</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="28" customHeight="1">
-      <x:c r="A26" s="239" t="str">
+    <x:row r="26" ht="27" customHeight="1">
+      <x:c r="A26" s="275" t="str">
         <x:v>Belo Horizonte e proximidades</x:v>
       </x:c>
-      <x:c r="B26" s="239"/>
+      <x:c r="B26" s="275"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
-      <x:c r="A27" s="236" t="n">
+      <x:c r="A27" s="271" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B27" s="236" t="str">
+      <x:c r="B27" s="271" t="str">
         <x:v>Cadence</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
-      <x:c r="A28" s="236" t="n">
+      <x:c r="A28" s="271" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B28" s="236" t="str">
+      <x:c r="B28" s="271" t="str">
         <x:v>RFIDO Design</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="28" customHeight="1">
-      <x:c r="A29" s="239" t="str">
+    <x:row r="29" ht="27" customHeight="1">
+      <x:c r="A29" s="275" t="str">
         <x:v>Campinas e proximidades</x:v>
       </x:c>
-      <x:c r="B29" s="239"/>
+      <x:c r="B29" s="275"/>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
-      <x:c r="A30" s="236" t="n">
+      <x:c r="A30" s="271" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B30" s="236" t="str">
+      <x:c r="B30" s="271" t="str">
         <x:v>Von Braun Labs</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
-      <x:c r="A31" s="236" t="n">
+      <x:c r="A31" s="271" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B31" s="236" t="str">
+      <x:c r="B31" s="271" t="str">
         <x:v>ADATA</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
-      <x:c r="A32" s="236" t="n">
+      <x:c r="A32" s="271" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B32" s="236" t="str">
+      <x:c r="B32" s="271" t="str">
         <x:v>HBR</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
-      <x:c r="A33" s="236" t="n">
+      <x:c r="A33" s="271" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B33" s="236" t="str">
+      <x:c r="B33" s="271" t="str">
         <x:v>HWiT</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
-      <x:c r="A34" s="236" t="n">
+      <x:c r="A34" s="271" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B34" s="236" t="str">
+      <x:c r="B34" s="271" t="str">
         <x:v>EnSilica</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
-      <x:c r="A35" s="236" t="n">
+      <x:c r="A35" s="271" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B35" s="236" t="str">
+      <x:c r="B35" s="271" t="str">
         <x:v>CPQD</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="24" customHeight="1">
-      <x:c r="A36" s="236" t="n">
+      <x:c r="A36" s="271" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B36" s="236" t="str">
+      <x:c r="B36" s="271" t="str">
         <x:v>Aedvices</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="24" customHeight="1">
-      <x:c r="A37" s="236" t="n">
+      <x:c r="A37" s="271" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B37" s="236" t="str">
+      <x:c r="B37" s="271" t="str">
         <x:v>Instituto de Pesquisas ELDORADO</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="24" customHeight="1">
-      <x:c r="A38" s="236" t="n">
+      <x:c r="A38" s="271" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B38" s="236" t="str">
+      <x:c r="B38" s="271" t="str">
         <x:v>Stoneridge</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="24" customHeight="1">
-      <x:c r="A39" s="236" t="n">
+      <x:c r="A39" s="271" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B39" s="236" t="str">
+      <x:c r="B39" s="271" t="str">
         <x:v>Valeo</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="24" customHeight="1">
-      <x:c r="A40" s="236" t="n">
+      <x:c r="A40" s="271" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B40" s="236" t="str">
+      <x:c r="B40" s="271" t="str">
         <x:v>Cadence</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="24" customHeight="1">
-      <x:c r="A41" s="236" t="n">
+      <x:c r="A41" s="271" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B41" s="236" t="str">
+      <x:c r="B41" s="271" t="str">
         <x:v>CNPEM</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="24" customHeight="1">
-      <x:c r="A42" s="236" t="n">
+      <x:c r="A42" s="271" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B42" s="236" t="str">
+      <x:c r="B42" s="271" t="str">
         <x:v>CTI Renato Archer</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="24" customHeight="1">
-      <x:c r="A43" s="236" t="n">
+      <x:c r="A43" s="271" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B43" s="236" t="str">
+      <x:c r="B43" s="271" t="str">
         <x:v>HCLTech</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="28" customHeight="1">
-      <x:c r="A44" s="239" t="str">
+    <x:row r="44" ht="27" customHeight="1">
+      <x:c r="A44" s="275" t="str">
         <x:v>Florianópolis</x:v>
       </x:c>
-      <x:c r="B44" s="239"/>
+      <x:c r="B44" s="275"/>
     </x:row>
     <x:row r="45" ht="24" customHeight="1">
-      <x:c r="A45" s="236" t="n">
+      <x:c r="A45" s="271" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B45" s="236" t="str">
+      <x:c r="B45" s="271" t="str">
         <x:v>Macnica DHW</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="24" customHeight="1">
-      <x:c r="A46" s="236" t="n">
+      <x:c r="A46" s="271" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B46" s="236" t="str">
+      <x:c r="B46" s="271" t="str">
         <x:v>Chipus</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="24" customHeight="1">
-      <x:c r="A47" s="236" t="n">
+      <x:c r="A47" s="271" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B47" s="236" t="str">
+      <x:c r="B47" s="271" t="str">
         <x:v>Synopsys</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="24" customHeight="1">
-      <x:c r="A48" s="236" t="n">
+      <x:c r="A48" s="271" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B48" s="236" t="str">
+      <x:c r="B48" s="271" t="str">
         <x:v>OSIRIS</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="24" customHeight="1">
-      <x:c r="A49" s="236" t="n">
+      <x:c r="A49" s="271" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B49" s="236" t="str">
+      <x:c r="B49" s="271" t="str">
         <x:v>Silicium</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="28" customHeight="1">
-      <x:c r="A50" s="239" t="str">
+    <x:row r="50" ht="27" customHeight="1">
+      <x:c r="A50" s="275" t="str">
         <x:v>Porto Alegre e proximidades</x:v>
       </x:c>
-      <x:c r="B50" s="239"/>
+      <x:c r="B50" s="275"/>
     </x:row>
     <x:row r="51" ht="24" customHeight="1">
-      <x:c r="A51" s="236" t="n">
+      <x:c r="A51" s="271" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B51" s="236" t="str">
+      <x:c r="B51" s="271" t="str">
         <x:v>Impinj</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="24" customHeight="1">
-      <x:c r="A52" s="236" t="n">
+      <x:c r="A52" s="271" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B52" s="236" t="str">
+      <x:c r="B52" s="271" t="str">
         <x:v>SILVACO</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="24" customHeight="1">
-      <x:c r="A53" s="236" t="n">
+      <x:c r="A53" s="271" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B53" s="236" t="str">
+      <x:c r="B53" s="271" t="str">
         <x:v>HCLTech</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="24" customHeight="1">
-      <x:c r="A54" s="236" t="n">
+      <x:c r="A54" s="271" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B54" s="236" t="str">
+      <x:c r="B54" s="271" t="str">
         <x:v>AEL Sistemas</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="24" customHeight="1">
-      <x:c r="A55" s="236" t="n">
+      <x:c r="A55" s="271" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B55" s="236" t="str">
+      <x:c r="B55" s="271" t="str">
         <x:v>Grupo Tellescom</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="24" customHeight="1">
-      <x:c r="A56" s="236" t="n">
+      <x:c r="A56" s="271" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B56" s="236" t="str">
+      <x:c r="B56" s="271" t="str">
         <x:v>Valeo</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="24" customHeight="1">
-      <x:c r="A57" s="236" t="n">
+      <x:c r="A57" s="271" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B57" s="236" t="str">
+      <x:c r="B57" s="271" t="str">
         <x:v>Instituto de Pesquisas ELDORADO</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="24" customHeight="1">
-      <x:c r="A58" s="236" t="n">
+      <x:c r="A58" s="271" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B58" s="236" t="str">
+      <x:c r="B58" s="271" t="str">
         <x:v>EnSilica</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="24" customHeight="1">
-      <x:c r="A59" s="236" t="n">
+      <x:c r="A59" s="271" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B59" s="236" t="str">
+      <x:c r="B59" s="271" t="str">
         <x:v>itt Chip — Unisinos</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="24" customHeight="1">
-      <x:c r="A60" s="236" t="n">
+      <x:c r="A60" s="271" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B60" s="236" t="str">
+      <x:c r="B60" s="271" t="str">
         <x:v>CEITEC</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="24" customHeight="1">
-      <x:c r="A61" s="236" t="n">
+      <x:c r="A61" s="271" t="n">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B61" s="236" t="str">
+      <x:c r="B61" s="271" t="str">
         <x:v>Instituto SENAI (RS)</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="24" customHeight="1">
-      <x:c r="A62" s="236" t="n">
+      <x:c r="A62" s="271" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B62" s="236" t="str">
+      <x:c r="B62" s="271" t="str">
         <x:v>InPlace</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="24" customHeight="1">
-      <x:c r="A63" s="236" t="n">
+      <x:c r="A63" s="271" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B63" s="236" t="str">
+      <x:c r="B63" s="271" t="str">
         <x:v>HT Micron</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="28" customHeight="1">
-      <x:c r="A64" s="239" t="str">
+    <x:row r="64" ht="27" customHeight="1">
+      <x:c r="A64" s="275" t="str">
         <x:v>Interior de São Paulo</x:v>
       </x:c>
-      <x:c r="B64" s="239"/>
+      <x:c r="B64" s="275"/>
     </x:row>
     <x:row r="65" ht="24" customHeight="1">
-      <x:c r="A65" s="236" t="n">
+      <x:c r="A65" s="271" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B65" s="236" t="str">
+      <x:c r="B65" s="271" t="str">
         <x:v>Macnica DHW</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="24" customHeight="1">
-      <x:c r="A66" s="236" t="n">
+      <x:c r="A66" s="271" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B66" s="236" t="str">
+      <x:c r="B66" s="271" t="str">
         <x:v>WG3</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="24" customHeight="1">
-      <x:c r="A67" s="236" t="n">
+      <x:c r="A67" s="271" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B67" s="236" t="str">
+      <x:c r="B67" s="271" t="str">
         <x:v>Chip Inventor</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="24" customHeight="1">
-      <x:c r="A68" s="236" t="n">
+      <x:c r="A68" s="271" t="n">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B68" s="236" t="str">
+      <x:c r="B68" s="271" t="str">
         <x:v>Beontag</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="24" customHeight="1">
-      <x:c r="A69" s="236" t="n">
+      <x:c r="A69" s="271" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B69" s="236" t="str">
+      <x:c r="B69" s="271" t="str">
         <x:v>SPICTEC</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="24" customHeight="1">
-      <x:c r="A70" s="236" t="n">
+      <x:c r="A70" s="271" t="n">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B70" s="236" t="str">
+      <x:c r="B70" s="271" t="str">
         <x:v>LSI-TEC</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="28" customHeight="1">
-      <x:c r="A71" s="239" t="str">
+    <x:row r="71" ht="24" customHeight="1">
+      <x:c r="A71" s="271" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B71" s="271" t="str">
+        <x:v>Zilia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="27" customHeight="1">
+      <x:c r="A72" s="275" t="str">
         <x:v>Curitiba e proximidades</x:v>
       </x:c>
-      <x:c r="B71" s="239"/>
-    </x:row>
-    <x:row r="72" ht="24" customHeight="1">
-      <x:c r="A72" s="236" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B72" s="236" t="str">
+      <x:c r="B72" s="275"/>
+    </x:row>
+    <x:row r="73" ht="24" customHeight="1">
+      <x:c r="A73" s="271" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B73" s="271" t="str">
         <x:v>HCLTech</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="24" customHeight="1">
-      <x:c r="A73" s="236" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B73" s="236" t="str">
+    <x:row r="74" ht="24" customHeight="1">
+      <x:c r="A74" s="271" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B74" s="271" t="str">
         <x:v>Thales Group</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="28" customHeight="1">
-      <x:c r="A74" s="239" t="str">
+    <x:row r="75" ht="24" customHeight="1">
+      <x:c r="A75" s="271" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B75" s="271" t="str">
+        <x:v>Lactec</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="27" customHeight="1">
+      <x:c r="A76" s="275" t="str">
         <x:v>Interior do Rio Grande do Sul</x:v>
       </x:c>
-      <x:c r="B74" s="239"/>
-    </x:row>
-    <x:row r="75" ht="24" customHeight="1">
-      <x:c r="A75" s="236" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B75" s="236" t="str">
+      <x:c r="B76" s="275"/>
+    </x:row>
+    <x:row r="77" ht="24" customHeight="1">
+      <x:c r="A77" s="271" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B77" s="271" t="str">
         <x:v>TUNA Semicondutores</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="24" customHeight="1">
-      <x:c r="A76" s="236" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B76" s="236" t="str">
+    <x:row r="78" ht="24" customHeight="1">
+      <x:c r="A78" s="271" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B78" s="271" t="str">
         <x:v>GMicro UFSM</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="28" customHeight="1">
-      <x:c r="A77" s="239" t="str">
+    <x:row r="79" ht="27" customHeight="1">
+      <x:c r="A79" s="275" t="str">
         <x:v>São José dos Campos e proximidades</x:v>
       </x:c>
-      <x:c r="B77" s="239"/>
-    </x:row>
-    <x:row r="78" ht="24" customHeight="1">
-      <x:c r="A78" s="236" t="n">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B78" s="236" t="str">
+      <x:c r="B79" s="275"/>
+    </x:row>
+    <x:row r="80" ht="24" customHeight="1">
+      <x:c r="A80" s="271" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B80" s="271" t="str">
         <x:v>Boeing</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="24" customHeight="1">
-      <x:c r="A79" s="236" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B79" s="236" t="str">
+    <x:row r="81" ht="24" customHeight="1">
+      <x:c r="A81" s="272" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B81" s="272" t="str">
         <x:v>Embraer</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="24" customHeight="1">
-      <x:c r="A80" s="236" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B80" s="236" t="str">
+    <x:row r="82" ht="24" customHeight="1">
+      <x:c r="A82" s="272" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B82" s="272" t="str">
         <x:v>Thales Group</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="24" customHeight="1">
-      <x:c r="A81" s="237" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B81" s="237" t="str">
+    <x:row r="83" ht="24" customHeight="1">
+      <x:c r="A83" s="272" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B83" s="272" t="str">
         <x:v>SIATT</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="24" customHeight="1">
-      <x:c r="A82" s="237" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B82" s="237" t="str">
+    <x:row r="84" ht="24" customHeight="1">
+      <x:c r="A84" s="272" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B84" s="272" t="str">
         <x:v>IACIT</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="24" customHeight="1">
-      <x:c r="A83" s="237" t="n">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B83" s="237" t="str">
+    <x:row r="85" ht="24" customHeight="1">
+      <x:c r="A85" s="272" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B85" s="272" t="str">
         <x:v>INPE</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="24" customHeight="1">
-      <x:c r="A84" s="237" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B84" s="237" t="str">
+    <x:row r="86" ht="24" customHeight="1">
+      <x:c r="A86" s="272" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B86" s="272" t="str">
         <x:v>Modirum | GESPI</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="15.75" customHeight="1">
-      <x:c r="A85" s="20"/>
-      <x:c r="B85" s="20"/>
-    </x:row>
-    <x:row r="86" ht="15.75" customHeight="1">
-      <x:c r="A86" s="20"/>
-      <x:c r="B86" s="20"/>
-    </x:row>
-    <x:row r="87" ht="15.75" customHeight="1">
-      <x:c r="A87" s="20"/>
-      <x:c r="B87" s="20"/>
+    <x:row r="87" ht="24" customHeight="1">
+      <x:c r="A87" s="272" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B87" s="272" t="str">
+        <x:v>Tecsys do Brasil</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="15.75" customHeight="1">
       <x:c r="A88" s="20"/>
@@ -6730,9 +6871,9 @@
     <x:mergeCell ref="A44:B44"/>
     <x:mergeCell ref="A50:B50"/>
     <x:mergeCell ref="A64:B64"/>
-    <x:mergeCell ref="A71:B71"/>
-    <x:mergeCell ref="A74:B74"/>
-    <x:mergeCell ref="A77:B77"/>
+    <x:mergeCell ref="A72:B72"/>
+    <x:mergeCell ref="A76:B76"/>
+    <x:mergeCell ref="A79:B79"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
